--- a/employment_forms/048_employee_complaint_form--employment_forms.xlsx
+++ b/employment_forms/048_employee_complaint_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>complaint_description</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Description of the complaint</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the issue you are experiencing</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>incident_description</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Incident description</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provide details about what happened</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>action_taken</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Action taken</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe the action taken by you</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>witness</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Witness</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>If there were any witnesses, please list their names</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>incident_date</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Incident date</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Date of the incident</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>incident_time</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Incident time</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Time of the incident</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,20 +687,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>incident_location</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Incident location</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Location of the incident</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +714,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>incident_date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Relationship between you and the complainant</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Who was the person you were interacting with?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,10 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>complaintant</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Type of incident</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Choose the type of incident that occurred</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -722,7 +758,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,10 +768,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>complaintant_relationship</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Incident details</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Provide any additional details you think are relevant</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -745,7 +785,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,333 +795,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>incident_type</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Supporting documentation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Upload any supporting documentation for this incident</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>incident_details</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>incident_details</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>supporting_document</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>supporting_document</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>supporting_document</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>supporting_document</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>supporting_document</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>supporting_document</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>supporting_document</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>action_taken</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>action_taken</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>action_taken</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>action_taken</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>action_taken</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +820,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,153 +848,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>employee_complaint_form_page_9_choices</t>
+          <t>employee_complaint_form_page_8_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'employee_complaint_form_page_9_complaintant_0',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'employee_complaint_form_page_9_complaintant_0', 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>employee_complaint_form_page_9_choices</t>
+          <t>employee_complaint_form_page_8_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'employee_complaint_form_page_9_complaintant_1',_'label':_'employee',_'value':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'employee_complaint_form_page_9_complaintant_1', 'label': 'Employee', 'value': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_complaint_form_page_9_choices</t>
+          <t>employee_complaint_form_page_8_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'employee_complaint_form_page_9_complaintant_2',_'label':_'supervisor',_'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'employee_complaint_form_page_9_complaintant_2', 'label': 'Supervisor', 'value': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>employee_complaint_form_page_10_choices</t>
+          <t>employee_complaint_form_page_9_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'employee_complaint_form_page_10_complaintant_relationship_0',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'employee_complaint_form_page_10_complaintant_relationship_0', 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employee_complaint_form_page_10_choices</t>
+          <t>employee_complaint_form_page_9_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'employee_complaint_form_page_10_complaintant_relationship_1',_'label':_'direct_supervisor',_'value':_'direct_supervisor'}</t>
+          <t>verbal_abuse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'employee_complaint_form_page_10_complaintant_relationship_1', 'label': 'Direct Supervisor', 'value': 'Direct Supervisor'}</t>
+          <t>Verbal Abuse</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employee_complaint_form_page_10_choices</t>
+          <t>employee_complaint_form_page_9_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'employee_complaint_form_page_10_complaintant_relationship_2',_'label':_'senior_manager',_'value':_'senior_manager'}</t>
+          <t>physical_threat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'employee_complaint_form_page_10_complaintant_relationship_2', 'label': 'Senior Manager', 'value': 'Senior Manager'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_complaint_form_page_11_incident_type_0',_'label':_'other',_'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'name': 'employee_complaint_form_page_11_incident_type_0', 'label': 'Other', 'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_complaint_form_page_11_incident_type_1',_'label':_'verbal_abuse',_'value':_'verbal'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'name': 'employee_complaint_form_page_11_incident_type_1', 'label': 'Verbal Abuse', 'value': 'Verbal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>employee_complaint_form_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_complaint_form_page_11_incident_type_2',_'label':_'physical_threat',_'value':_'physical'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'name': 'employee_complaint_form_page_11_incident_type_2', 'label': 'Physical Threat', 'value': 'Physical'}</t>
+          <t>Physical Threat</t>
         </is>
       </c>
     </row>
